--- a/Assets/Data/Excel/RandomSpawnConfig.xlsx
+++ b/Assets/Data/Excel/RandomSpawnConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9976DBBB-FF4D-4724-B852-0F30EB214BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91C8487-A4D9-4B4F-A030-CA657443BD4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32550" yWindow="3300" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18360" yWindow="3690" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>Id</t>
   </si>
@@ -394,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="12.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="12.75" style="1"/>
@@ -456,6 +456,34 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>102</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>103</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
